--- a/backend/wp_templates/I/I3 商誉.xlsx
+++ b/backend/wp_templates/I/I3 商誉.xlsx
@@ -16577,8 +16577,6 @@
   </mergeCells>
   <phoneticPr fontId="36" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D60" r:id="rId1"/>
-    <hyperlink ref="D61" r:id="rId2"/>
     <hyperlink ref="L3" location="底稿目录!D12" display="I3-6"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
@@ -19142,58 +19140,6 @@
   </rowBreaks>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
-  <oleObjects>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="6145" r:id="rId4">
-          <objectPr defaultSize="0" altText="" r:id="rId5">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>99060</xdr:colOff>
-                <xdr:row>72</xdr:row>
-                <xdr:rowOff>30480</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>548640</xdr:colOff>
-                <xdr:row>75</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="6145" r:id="rId4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="6146" r:id="rId6">
-          <objectPr defaultSize="0" altText="" r:id="rId7">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>662940</xdr:colOff>
-                <xdr:row>72</xdr:row>
-                <xdr:rowOff>144780</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>205740</xdr:colOff>
-                <xdr:row>74</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="6146" r:id="rId6"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </oleObjects>
 </worksheet>
 </file>
 
@@ -29412,383 +29358,6 @@
   </headerFooter>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
-  <oleObjects>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="3073" r:id="rId4">
-          <objectPr defaultSize="0" altText="" r:id="rId5">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>99060</xdr:colOff>
-                <xdr:row>26</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>624840</xdr:colOff>
-                <xdr:row>26</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="3073" r:id="rId4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="3074" r:id="rId6">
-          <objectPr defaultSize="0" altText="" r:id="rId7">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>281940</xdr:colOff>
-                <xdr:row>72</xdr:row>
-                <xdr:rowOff>22860</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>259080</xdr:colOff>
-                <xdr:row>75</xdr:row>
-                <xdr:rowOff>22860</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="3074" r:id="rId6"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="3075" r:id="rId8">
-          <objectPr defaultSize="0" altText="" r:id="rId9">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>129540</xdr:colOff>
-                <xdr:row>79</xdr:row>
-                <xdr:rowOff>22860</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>571500</xdr:colOff>
-                <xdr:row>79</xdr:row>
-                <xdr:rowOff>220980</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="3075" r:id="rId8"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="3076" r:id="rId10">
-          <objectPr defaultSize="0" altText="" r:id="rId11">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>106680</xdr:colOff>
-                <xdr:row>79</xdr:row>
-                <xdr:rowOff>22860</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>556260</xdr:colOff>
-                <xdr:row>79</xdr:row>
-                <xdr:rowOff>220980</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="3076" r:id="rId10"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="3077" r:id="rId12">
-          <objectPr defaultSize="0" altText="" r:id="rId13">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>79</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>10</xdr:col>
-                <xdr:colOff>495300</xdr:colOff>
-                <xdr:row>79</xdr:row>
-                <xdr:rowOff>243840</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="3077" r:id="rId12"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="3078" r:id="rId14">
-          <objectPr defaultSize="0" altText="" r:id="rId15">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>99060</xdr:colOff>
-                <xdr:row>79</xdr:row>
-                <xdr:rowOff>22860</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>586740</xdr:colOff>
-                <xdr:row>79</xdr:row>
-                <xdr:rowOff>243840</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="3078" r:id="rId14"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="3079" r:id="rId16">
-          <objectPr defaultSize="0" altText="" r:id="rId17">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>12</xdr:col>
-                <xdr:colOff>144780</xdr:colOff>
-                <xdr:row>79</xdr:row>
-                <xdr:rowOff>22860</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>12</xdr:col>
-                <xdr:colOff>632460</xdr:colOff>
-                <xdr:row>79</xdr:row>
-                <xdr:rowOff>243840</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="3079" r:id="rId16"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="3080" r:id="rId18">
-          <objectPr defaultSize="0" altText="" r:id="rId19">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>304800</xdr:colOff>
-                <xdr:row>90</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>312420</xdr:colOff>
-                <xdr:row>94</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="3080" r:id="rId18"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="3081" r:id="rId20">
-          <objectPr defaultSize="0" altText="" r:id="rId21">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>251460</xdr:colOff>
-                <xdr:row>90</xdr:row>
-                <xdr:rowOff>30480</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>121920</xdr:colOff>
-                <xdr:row>94</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="3081" r:id="rId20"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="3082" r:id="rId22">
-          <objectPr defaultSize="0" altText="" r:id="rId23">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>335280</xdr:colOff>
-                <xdr:row>94</xdr:row>
-                <xdr:rowOff>167640</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>190500</xdr:colOff>
-                <xdr:row>96</xdr:row>
-                <xdr:rowOff>121920</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="3082" r:id="rId22"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="3083" r:id="rId24">
-          <objectPr defaultSize="0" altText="" r:id="rId25">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>220980</xdr:colOff>
-                <xdr:row>94</xdr:row>
-                <xdr:rowOff>228600</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>213360</xdr:colOff>
-                <xdr:row>96</xdr:row>
-                <xdr:rowOff>167640</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="3083" r:id="rId24"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="3084" r:id="rId26">
-          <objectPr defaultSize="0" altText="" r:id="rId27">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>167640</xdr:colOff>
-                <xdr:row>79</xdr:row>
-                <xdr:rowOff>15240</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>358140</xdr:colOff>
-                <xdr:row>79</xdr:row>
-                <xdr:rowOff>259080</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="3084" r:id="rId26"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="3085" r:id="rId28">
-          <objectPr defaultSize="0" altText="" r:id="rId29">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>106680</xdr:colOff>
-                <xdr:row>79</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>419100</xdr:colOff>
-                <xdr:row>79</xdr:row>
-                <xdr:rowOff>213360</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="3085" r:id="rId28"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="3086" r:id="rId30">
-          <objectPr defaultSize="0" altText="" r:id="rId31">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>243840</xdr:colOff>
-                <xdr:row>54</xdr:row>
-                <xdr:rowOff>106680</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>175260</xdr:colOff>
-                <xdr:row>56</xdr:row>
-                <xdr:rowOff>137160</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="3086" r:id="rId30"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Equation.3" shapeId="3087" r:id="rId32">
-          <objectPr defaultSize="0" altText="" r:id="rId33">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>586740</xdr:colOff>
-                <xdr:row>54</xdr:row>
-                <xdr:rowOff>167640</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>297180</xdr:colOff>
-                <xdr:row>55</xdr:row>
-                <xdr:rowOff>190500</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Equation.3" shapeId="3087" r:id="rId32"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </oleObjects>
 </worksheet>
 </file>
 

--- a/backend/wp_templates/I/I3 商誉.xlsx
+++ b/backend/wp_templates/I/I3 商誉.xlsx
@@ -33819,7 +33819,9 @@
       <c r="F14" s="236"/>
       <c r="G14" s="235"/>
       <c r="H14" s="236"/>
-      <c r="I14" s="221"/>
+      <c r="I14" s="221">
+        <f>SUM(D14:E14)-G14</f>
+      </c>
       <c r="J14" s="235"/>
       <c r="K14" s="235"/>
       <c r="L14" s="235"/>
@@ -34481,7 +34483,7 @@
         <v>0</v>
       </c>
       <c r="AA23" s="369">
-        <f t="shared" ref="AA23:AD23" si="21">SUM(AA27:AA30)</f>
+        <f t="shared" ref="AA23:AD23" si="21">SUM(AA14:AA22)</f>
         <v>0</v>
       </c>
       <c r="AB23" s="369">
